--- a/output/pdf_financials_xlsx/AWCM.xlsx
+++ b/output/pdf_financials_xlsx/AWCM.xlsx
@@ -2205,16 +2205,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.454755</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.728655</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.780655</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.780655</v>
       </c>
     </row>
     <row r="93">
@@ -3704,7 +3704,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4168,7 +4172,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>1.454755</v>
       </c>

--- a/output/pdf_financials_xlsx/AWCM.xlsx
+++ b/output/pdf_financials_xlsx/AWCM.xlsx
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.430681</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.419198</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.03266</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.034839</v>
       </c>
     </row>
     <row r="35">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.430681</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.258831</v>
+        <v>0.678029</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.075935</v>
+        <v>0.108595</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.311167</v>
+        <v>0.346006</v>
       </c>
     </row>
     <row r="37">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.465354</v>
+        <v>0.034673</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.419198</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.074721</v>
+        <v>0.042061</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.034907</v>
+        <v>6.8e-05</v>
       </c>
     </row>
     <row r="49">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.057875</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.053875</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -2820,13 +2820,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.057875</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.053875</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3362,7 +3362,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.021927</v>
       </c>
@@ -4820,7 +4824,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>-0.057875</v>
       </c>
@@ -5788,7 +5796,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>-0.019177</v>
       </c>

--- a/output/pdf_financials_xlsx/AWCM.xlsx
+++ b/output/pdf_financials_xlsx/AWCM.xlsx
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-9.602702000000001</v>
+        <v>-9.564401</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-4.2591</v>
+        <v>-4.153834</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-2.158323</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.038301</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.105266</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -4894,7 +4894,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -5872,7 +5876,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>5.73</v>
       </c>
@@ -7150,7 +7158,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E118" s="5" t="n">
         <v>-9.564401</v>
       </c>
@@ -7182,7 +7194,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>-0.038301</v>
       </c>
